--- a/data/trans_bre/P1426-Clase-trans_bre.xlsx
+++ b/data/trans_bre/P1426-Clase-trans_bre.xlsx
@@ -606,7 +606,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>-1,05</t>
+          <t>-0,81</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -621,7 +621,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-24,77%</t>
+          <t>-19,52%</t>
         </is>
       </c>
     </row>
@@ -634,17 +634,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,71</t>
+          <t>0,07; 2,77</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-1,71; 2,19</t>
+          <t>-1,53; 2,3</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-3,08; 0,92</t>
+          <t>-2,8; 1,18</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -654,12 +654,12 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-83,76; 405,43</t>
+          <t>-80,89; 373,25</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-58,98; 29,89</t>
+          <t>-52,98; 41,81</t>
         </is>
       </c>
     </row>
@@ -686,7 +686,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>-2,59</t>
+          <t>-2,48</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -701,7 +701,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-53,52%</t>
+          <t>-52,86%</t>
         </is>
       </c>
     </row>
@@ -714,22 +714,22 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-1,31; 2,58</t>
+          <t>-1,28; 2,7</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-0,81; 2,48</t>
+          <t>-0,61; 2,54</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-4,72; -0,72</t>
+          <t>-4,49; -0,55</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-83,21; 494,92</t>
+          <t>-83,31; 708,19</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -739,7 +739,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-76,69; -15,68</t>
+          <t>-74,82; -4,65</t>
         </is>
       </c>
     </row>
@@ -766,7 +766,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>0,95</t>
+          <t>-0,78</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -781,7 +781,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>29,29%</t>
+          <t>-16,28%</t>
         </is>
       </c>
     </row>
@@ -794,32 +794,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-2,02; 2,01</t>
+          <t>-2,32; 1,98</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,33; 4,49</t>
+          <t>-1,53; 4,65</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,89; 5,11</t>
+          <t>-3,34; 2,28</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-80,38; 164,73</t>
+          <t>-81,4; 165,96</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-65,26; 558,47</t>
+          <t>-70,23; 437,94</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-37,34; 335,27</t>
+          <t>-59,18; 65,12</t>
         </is>
       </c>
     </row>
@@ -846,7 +846,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>-3,33</t>
+          <t>-2,7</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -861,7 +861,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-55,99%</t>
+          <t>-45,69%</t>
         </is>
       </c>
     </row>
@@ -874,32 +874,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-1,73; 0,46</t>
+          <t>-1,75; 0,41</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-1,41; 0,81</t>
+          <t>-1,32; 0,91</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-5,26; -1,82</t>
+          <t>-4,16; -1,19</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-76,7; 47,89</t>
+          <t>-78,76; 47,43</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-66,06; 74,65</t>
+          <t>-63,05; 76,8</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-79,73; -35,4</t>
+          <t>-62,26; -24,0</t>
         </is>
       </c>
     </row>
@@ -926,7 +926,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0,89</t>
+          <t>2,24</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -941,7 +941,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>17,26%</t>
+          <t>51,14%</t>
         </is>
       </c>
     </row>
@@ -954,39 +954,39 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-2,53; 0,64</t>
+          <t>-2,58; 0,62</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-1,69; 1,17</t>
+          <t>-1,76; 1,18</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-1,79; 3,09</t>
+          <t>0,06; 4,29</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-73,34; 59,66</t>
+          <t>-74,67; 53,42</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-62,84; 88,68</t>
+          <t>-62,95; 100,14</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-25,22; 78,28</t>
+          <t>0,24; 132,87</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1006,7 +1006,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>5,83</t>
+          <t>5,62</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>780,54%</t>
+          <t>705,42%</t>
         </is>
       </c>
     </row>
@@ -1034,17 +1034,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-0,16; 3,45</t>
+          <t>-0,34; 3,45</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>2,12; 4,32</t>
+          <t>2,05; 4,25</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>4,22; 7,63</t>
+          <t>3,86; 7,14</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -1059,7 +1059,7 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>180,24; 2995,94</t>
+          <t>164,78; 2895,6</t>
         </is>
       </c>
     </row>
@@ -1086,7 +1086,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>-0,15</t>
+          <t>-0,02</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-3,32%</t>
+          <t>-0,45%</t>
         </is>
       </c>
     </row>
@@ -1114,32 +1114,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,31; 0,96</t>
+          <t>-0,35; 0,94</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-0,06; 1,24</t>
+          <t>-0,03; 1,32</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-1,22; 0,99</t>
+          <t>-0,87; 0,79</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-18,51; 81,08</t>
+          <t>-17,92; 77,06</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-4,13; 106,82</t>
+          <t>-1,9; 115,05</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-24,34; 25,38</t>
+          <t>-16,88; 18,54</t>
         </is>
       </c>
     </row>
